--- a/artfynd/A 36879-2023 artfynd.xlsx
+++ b/artfynd/A 36879-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 36879-2023 artfynd.xlsx
+++ b/artfynd/A 36879-2023 artfynd.xlsx
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120058981</v>
+        <v>120058970</v>
       </c>
       <c r="B17" t="n">
-        <v>77458</v>
+        <v>79144</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2281,21 +2281,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>684561</v>
+        <v>684520</v>
       </c>
       <c r="R17" t="n">
-        <v>7393342</v>
+        <v>7393345</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2367,10 +2367,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120058978</v>
+        <v>120058974</v>
       </c>
       <c r="B18" t="n">
-        <v>91840</v>
+        <v>57463</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2379,25 +2379,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2407,10 +2407,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>684521</v>
+        <v>684560</v>
       </c>
       <c r="R18" t="n">
-        <v>7393403</v>
+        <v>7393340</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2469,10 +2469,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120058977</v>
+        <v>120058982</v>
       </c>
       <c r="B19" t="n">
-        <v>91352</v>
+        <v>77910</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2485,21 +2485,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2014</v>
+        <v>6437</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>684401</v>
+        <v>684559</v>
       </c>
       <c r="R19" t="n">
-        <v>7393386</v>
+        <v>7393341</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2571,10 +2571,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120058976</v>
+        <v>120058977</v>
       </c>
       <c r="B20" t="n">
-        <v>79511</v>
+        <v>91352</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2583,25 +2583,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6456</v>
+        <v>2014</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2611,10 +2611,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>684521</v>
+        <v>684401</v>
       </c>
       <c r="R20" t="n">
-        <v>7393348</v>
+        <v>7393386</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2673,10 +2673,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120058982</v>
+        <v>120058978</v>
       </c>
       <c r="B21" t="n">
-        <v>77910</v>
+        <v>91840</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2685,25 +2685,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>684559</v>
+        <v>684521</v>
       </c>
       <c r="R21" t="n">
-        <v>7393341</v>
+        <v>7393403</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2775,10 +2775,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120058974</v>
+        <v>120058983</v>
       </c>
       <c r="B22" t="n">
-        <v>57463</v>
+        <v>77910</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2791,21 +2791,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>6437</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2815,10 +2815,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>684560</v>
+        <v>684631</v>
       </c>
       <c r="R22" t="n">
-        <v>7393340</v>
+        <v>7393313</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2877,10 +2877,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120058983</v>
+        <v>120058981</v>
       </c>
       <c r="B23" t="n">
-        <v>77910</v>
+        <v>77458</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2893,21 +2893,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6437</v>
+        <v>6487</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2917,10 +2917,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>684631</v>
+        <v>684561</v>
       </c>
       <c r="R23" t="n">
-        <v>7393313</v>
+        <v>7393342</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2979,10 +2979,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120058970</v>
+        <v>120058975</v>
       </c>
       <c r="B24" t="n">
-        <v>79144</v>
+        <v>79511</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2991,25 +2991,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6456</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3019,10 +3019,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>684520</v>
+        <v>684411</v>
       </c>
       <c r="R24" t="n">
-        <v>7393345</v>
+        <v>7393343</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3081,7 +3081,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120058975</v>
+        <v>120058976</v>
       </c>
       <c r="B25" t="n">
         <v>79511</v>
@@ -3121,10 +3121,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>684411</v>
+        <v>684521</v>
       </c>
       <c r="R25" t="n">
-        <v>7393343</v>
+        <v>7393348</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 36879-2023 artfynd.xlsx
+++ b/artfynd/A 36879-2023 artfynd.xlsx
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120058970</v>
+        <v>120058976</v>
       </c>
       <c r="B17" t="n">
-        <v>79144</v>
+        <v>79511</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2277,25 +2277,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6456</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>684520</v>
+        <v>684521</v>
       </c>
       <c r="R17" t="n">
-        <v>7393345</v>
+        <v>7393348</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2367,10 +2367,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120058974</v>
+        <v>120058970</v>
       </c>
       <c r="B18" t="n">
-        <v>57463</v>
+        <v>79144</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2383,21 +2383,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2407,10 +2407,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>684560</v>
+        <v>684520</v>
       </c>
       <c r="R18" t="n">
-        <v>7393340</v>
+        <v>7393345</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2469,10 +2469,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120058982</v>
+        <v>120058975</v>
       </c>
       <c r="B19" t="n">
-        <v>77910</v>
+        <v>79511</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2481,25 +2481,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6437</v>
+        <v>6456</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>684559</v>
+        <v>684411</v>
       </c>
       <c r="R19" t="n">
-        <v>7393341</v>
+        <v>7393343</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2571,10 +2571,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120058977</v>
+        <v>120058982</v>
       </c>
       <c r="B20" t="n">
-        <v>91352</v>
+        <v>77910</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2587,21 +2587,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2014</v>
+        <v>6437</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2611,10 +2611,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>684401</v>
+        <v>684559</v>
       </c>
       <c r="R20" t="n">
-        <v>7393386</v>
+        <v>7393341</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2673,10 +2673,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120058978</v>
+        <v>120058981</v>
       </c>
       <c r="B21" t="n">
-        <v>91840</v>
+        <v>77458</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2685,25 +2685,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>684521</v>
+        <v>684561</v>
       </c>
       <c r="R21" t="n">
-        <v>7393403</v>
+        <v>7393342</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2877,10 +2877,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120058981</v>
+        <v>120058974</v>
       </c>
       <c r="B23" t="n">
-        <v>77458</v>
+        <v>57463</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2893,21 +2893,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6487</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2917,10 +2917,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>684561</v>
+        <v>684560</v>
       </c>
       <c r="R23" t="n">
-        <v>7393342</v>
+        <v>7393340</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2979,10 +2979,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120058975</v>
+        <v>120058977</v>
       </c>
       <c r="B24" t="n">
-        <v>79511</v>
+        <v>91352</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2991,25 +2991,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6456</v>
+        <v>2014</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3019,10 +3019,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>684411</v>
+        <v>684401</v>
       </c>
       <c r="R24" t="n">
-        <v>7393343</v>
+        <v>7393386</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3081,10 +3081,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120058976</v>
+        <v>120058978</v>
       </c>
       <c r="B25" t="n">
-        <v>79511</v>
+        <v>91840</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3097,21 +3097,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6456</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3124,7 +3124,7 @@
         <v>684521</v>
       </c>
       <c r="R25" t="n">
-        <v>7393348</v>
+        <v>7393403</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 36879-2023 artfynd.xlsx
+++ b/artfynd/A 36879-2023 artfynd.xlsx
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120058976</v>
+        <v>120058983</v>
       </c>
       <c r="B17" t="n">
-        <v>79511</v>
+        <v>77910</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2277,25 +2277,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6456</v>
+        <v>6437</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>684521</v>
+        <v>684631</v>
       </c>
       <c r="R17" t="n">
-        <v>7393348</v>
+        <v>7393313</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2367,10 +2367,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120058970</v>
+        <v>120058978</v>
       </c>
       <c r="B18" t="n">
-        <v>79144</v>
+        <v>91840</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2379,25 +2379,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2407,10 +2407,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>684520</v>
+        <v>684521</v>
       </c>
       <c r="R18" t="n">
-        <v>7393345</v>
+        <v>7393403</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2469,7 +2469,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120058975</v>
+        <v>120058976</v>
       </c>
       <c r="B19" t="n">
         <v>79511</v>
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>684411</v>
+        <v>684521</v>
       </c>
       <c r="R19" t="n">
-        <v>7393343</v>
+        <v>7393348</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2571,10 +2571,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120058982</v>
+        <v>120058975</v>
       </c>
       <c r="B20" t="n">
-        <v>77910</v>
+        <v>79511</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2583,25 +2583,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6437</v>
+        <v>6456</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2611,10 +2611,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>684559</v>
+        <v>684411</v>
       </c>
       <c r="R20" t="n">
-        <v>7393341</v>
+        <v>7393343</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2775,10 +2775,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120058983</v>
+        <v>120058970</v>
       </c>
       <c r="B22" t="n">
-        <v>77910</v>
+        <v>79144</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2791,21 +2791,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2815,10 +2815,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>684631</v>
+        <v>684520</v>
       </c>
       <c r="R22" t="n">
-        <v>7393313</v>
+        <v>7393345</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2877,10 +2877,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120058974</v>
+        <v>120058982</v>
       </c>
       <c r="B23" t="n">
-        <v>57463</v>
+        <v>77910</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2893,21 +2893,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>6437</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2917,10 +2917,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>684560</v>
+        <v>684559</v>
       </c>
       <c r="R23" t="n">
-        <v>7393340</v>
+        <v>7393341</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3081,10 +3081,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120058978</v>
+        <v>120058974</v>
       </c>
       <c r="B25" t="n">
-        <v>91840</v>
+        <v>57463</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3093,25 +3093,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3121,10 +3121,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>684521</v>
+        <v>684560</v>
       </c>
       <c r="R25" t="n">
-        <v>7393403</v>
+        <v>7393340</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 36879-2023 artfynd.xlsx
+++ b/artfynd/A 36879-2023 artfynd.xlsx
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120058983</v>
+        <v>120058970</v>
       </c>
       <c r="B17" t="n">
-        <v>77910</v>
+        <v>79160</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2281,21 +2281,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>684631</v>
+        <v>684520</v>
       </c>
       <c r="R17" t="n">
-        <v>7393313</v>
+        <v>7393345</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2367,10 +2367,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120058978</v>
+        <v>120058983</v>
       </c>
       <c r="B18" t="n">
-        <v>91840</v>
+        <v>77926</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2379,25 +2379,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2407,10 +2407,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>684521</v>
+        <v>684631</v>
       </c>
       <c r="R18" t="n">
-        <v>7393403</v>
+        <v>7393313</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2472,7 +2472,7 @@
         <v>120058976</v>
       </c>
       <c r="B19" t="n">
-        <v>79511</v>
+        <v>79527</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2571,10 +2571,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120058975</v>
+        <v>120058977</v>
       </c>
       <c r="B20" t="n">
-        <v>79511</v>
+        <v>91370</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2583,25 +2583,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6456</v>
+        <v>2014</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2611,10 +2611,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>684411</v>
+        <v>684401</v>
       </c>
       <c r="R20" t="n">
-        <v>7393343</v>
+        <v>7393386</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2673,10 +2673,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120058981</v>
+        <v>120058978</v>
       </c>
       <c r="B21" t="n">
-        <v>77458</v>
+        <v>91858</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2685,25 +2685,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>684561</v>
+        <v>684521</v>
       </c>
       <c r="R21" t="n">
-        <v>7393342</v>
+        <v>7393403</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2775,10 +2775,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120058970</v>
+        <v>120058974</v>
       </c>
       <c r="B22" t="n">
-        <v>79144</v>
+        <v>57473</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2791,21 +2791,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2815,10 +2815,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>684520</v>
+        <v>684560</v>
       </c>
       <c r="R22" t="n">
-        <v>7393345</v>
+        <v>7393340</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2877,10 +2877,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120058982</v>
+        <v>120058975</v>
       </c>
       <c r="B23" t="n">
-        <v>77910</v>
+        <v>79527</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2889,25 +2889,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6437</v>
+        <v>6456</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2917,10 +2917,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>684559</v>
+        <v>684411</v>
       </c>
       <c r="R23" t="n">
-        <v>7393341</v>
+        <v>7393343</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2979,10 +2979,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120058977</v>
+        <v>120058981</v>
       </c>
       <c r="B24" t="n">
-        <v>91352</v>
+        <v>77474</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2995,21 +2995,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2014</v>
+        <v>6487</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3019,10 +3019,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>684401</v>
+        <v>684561</v>
       </c>
       <c r="R24" t="n">
-        <v>7393386</v>
+        <v>7393342</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3081,10 +3081,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120058974</v>
+        <v>120058982</v>
       </c>
       <c r="B25" t="n">
-        <v>57463</v>
+        <v>77926</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3097,21 +3097,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>6437</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3121,10 +3121,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>684560</v>
+        <v>684559</v>
       </c>
       <c r="R25" t="n">
-        <v>7393340</v>
+        <v>7393341</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 36879-2023 artfynd.xlsx
+++ b/artfynd/A 36879-2023 artfynd.xlsx
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120058970</v>
+        <v>120058975</v>
       </c>
       <c r="B17" t="n">
-        <v>79160</v>
+        <v>79527</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2277,25 +2277,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6456</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>684520</v>
+        <v>684411</v>
       </c>
       <c r="R17" t="n">
-        <v>7393345</v>
+        <v>7393343</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2367,10 +2367,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120058983</v>
+        <v>120058974</v>
       </c>
       <c r="B18" t="n">
-        <v>77926</v>
+        <v>57473</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2383,21 +2383,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6437</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2407,10 +2407,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>684631</v>
+        <v>684560</v>
       </c>
       <c r="R18" t="n">
-        <v>7393313</v>
+        <v>7393340</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2469,10 +2469,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120058976</v>
+        <v>120058978</v>
       </c>
       <c r="B19" t="n">
-        <v>79527</v>
+        <v>91858</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2485,21 +2485,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6456</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2512,7 +2512,7 @@
         <v>684521</v>
       </c>
       <c r="R19" t="n">
-        <v>7393348</v>
+        <v>7393403</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2571,10 +2571,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120058977</v>
+        <v>120058970</v>
       </c>
       <c r="B20" t="n">
-        <v>91370</v>
+        <v>79160</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2587,21 +2587,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2014</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2611,10 +2611,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>684401</v>
+        <v>684520</v>
       </c>
       <c r="R20" t="n">
-        <v>7393386</v>
+        <v>7393345</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2673,10 +2673,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120058978</v>
+        <v>120058977</v>
       </c>
       <c r="B21" t="n">
-        <v>91858</v>
+        <v>91370</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2685,25 +2685,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>2014</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>684521</v>
+        <v>684401</v>
       </c>
       <c r="R21" t="n">
-        <v>7393403</v>
+        <v>7393386</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2775,10 +2775,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120058974</v>
+        <v>120058976</v>
       </c>
       <c r="B22" t="n">
-        <v>57473</v>
+        <v>79527</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2787,25 +2787,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>6456</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2815,10 +2815,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>684560</v>
+        <v>684521</v>
       </c>
       <c r="R22" t="n">
-        <v>7393340</v>
+        <v>7393348</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2877,10 +2877,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120058975</v>
+        <v>120058982</v>
       </c>
       <c r="B23" t="n">
-        <v>79527</v>
+        <v>77926</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2889,25 +2889,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6456</v>
+        <v>6437</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2917,10 +2917,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>684411</v>
+        <v>684559</v>
       </c>
       <c r="R23" t="n">
-        <v>7393343</v>
+        <v>7393341</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2979,10 +2979,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120058981</v>
+        <v>120058983</v>
       </c>
       <c r="B24" t="n">
-        <v>77474</v>
+        <v>77926</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2995,21 +2995,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6487</v>
+        <v>6437</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3019,10 +3019,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>684561</v>
+        <v>684631</v>
       </c>
       <c r="R24" t="n">
-        <v>7393342</v>
+        <v>7393313</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3081,10 +3081,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120058982</v>
+        <v>120058981</v>
       </c>
       <c r="B25" t="n">
-        <v>77926</v>
+        <v>77474</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3097,21 +3097,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6437</v>
+        <v>6487</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3121,10 +3121,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>684559</v>
+        <v>684561</v>
       </c>
       <c r="R25" t="n">
-        <v>7393341</v>
+        <v>7393342</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 36879-2023 artfynd.xlsx
+++ b/artfynd/A 36879-2023 artfynd.xlsx
@@ -2571,10 +2571,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120058970</v>
+        <v>120058977</v>
       </c>
       <c r="B20" t="n">
-        <v>79160</v>
+        <v>91370</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2587,21 +2587,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>2014</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2611,10 +2611,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>684520</v>
+        <v>684401</v>
       </c>
       <c r="R20" t="n">
-        <v>7393345</v>
+        <v>7393386</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2673,10 +2673,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120058977</v>
+        <v>120058970</v>
       </c>
       <c r="B21" t="n">
-        <v>91370</v>
+        <v>79160</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2689,21 +2689,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2014</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>684401</v>
+        <v>684520</v>
       </c>
       <c r="R21" t="n">
-        <v>7393386</v>
+        <v>7393345</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 36879-2023 artfynd.xlsx
+++ b/artfynd/A 36879-2023 artfynd.xlsx
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120058975</v>
+        <v>120058970</v>
       </c>
       <c r="B17" t="n">
-        <v>79527</v>
+        <v>79160</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2277,25 +2277,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6456</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>684411</v>
+        <v>684520</v>
       </c>
       <c r="R17" t="n">
-        <v>7393343</v>
+        <v>7393345</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2367,10 +2367,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120058974</v>
+        <v>120058982</v>
       </c>
       <c r="B18" t="n">
-        <v>57473</v>
+        <v>77926</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2383,21 +2383,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>6437</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2407,10 +2407,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>684560</v>
+        <v>684559</v>
       </c>
       <c r="R18" t="n">
-        <v>7393340</v>
+        <v>7393341</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2469,10 +2469,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120058978</v>
+        <v>120058975</v>
       </c>
       <c r="B19" t="n">
-        <v>91858</v>
+        <v>79527</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2485,21 +2485,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6456</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>684521</v>
+        <v>684411</v>
       </c>
       <c r="R19" t="n">
-        <v>7393403</v>
+        <v>7393343</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2571,10 +2571,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120058977</v>
+        <v>120058976</v>
       </c>
       <c r="B20" t="n">
-        <v>91370</v>
+        <v>79527</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2583,25 +2583,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2014</v>
+        <v>6456</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2611,10 +2611,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>684401</v>
+        <v>684521</v>
       </c>
       <c r="R20" t="n">
-        <v>7393386</v>
+        <v>7393348</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2673,10 +2673,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120058970</v>
+        <v>120058983</v>
       </c>
       <c r="B21" t="n">
-        <v>79160</v>
+        <v>77926</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2689,21 +2689,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>684520</v>
+        <v>684631</v>
       </c>
       <c r="R21" t="n">
-        <v>7393345</v>
+        <v>7393313</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2775,10 +2775,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120058976</v>
+        <v>120058977</v>
       </c>
       <c r="B22" t="n">
-        <v>79527</v>
+        <v>91370</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2787,25 +2787,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>2014</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2815,10 +2815,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>684521</v>
+        <v>684401</v>
       </c>
       <c r="R22" t="n">
-        <v>7393348</v>
+        <v>7393386</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2877,10 +2877,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120058982</v>
+        <v>120058974</v>
       </c>
       <c r="B23" t="n">
-        <v>77926</v>
+        <v>57473</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2893,21 +2893,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6437</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2917,10 +2917,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>684559</v>
+        <v>684560</v>
       </c>
       <c r="R23" t="n">
-        <v>7393341</v>
+        <v>7393340</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2979,10 +2979,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120058983</v>
+        <v>120058978</v>
       </c>
       <c r="B24" t="n">
-        <v>77926</v>
+        <v>91858</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2991,25 +2991,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3019,10 +3019,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>684631</v>
+        <v>684521</v>
       </c>
       <c r="R24" t="n">
-        <v>7393313</v>
+        <v>7393403</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 36879-2023 artfynd.xlsx
+++ b/artfynd/A 36879-2023 artfynd.xlsx
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120058970</v>
+        <v>120058978</v>
       </c>
       <c r="B17" t="n">
-        <v>79160</v>
+        <v>91858</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2277,25 +2277,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>684520</v>
+        <v>684521</v>
       </c>
       <c r="R17" t="n">
-        <v>7393345</v>
+        <v>7393403</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2367,10 +2367,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120058982</v>
+        <v>120058970</v>
       </c>
       <c r="B18" t="n">
-        <v>77926</v>
+        <v>79160</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2383,21 +2383,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2407,10 +2407,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>684559</v>
+        <v>684520</v>
       </c>
       <c r="R18" t="n">
-        <v>7393341</v>
+        <v>7393345</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2469,10 +2469,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120058975</v>
+        <v>120058983</v>
       </c>
       <c r="B19" t="n">
-        <v>79527</v>
+        <v>77926</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2481,25 +2481,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6456</v>
+        <v>6437</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>684411</v>
+        <v>684631</v>
       </c>
       <c r="R19" t="n">
-        <v>7393343</v>
+        <v>7393313</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2673,10 +2673,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120058983</v>
+        <v>120058977</v>
       </c>
       <c r="B21" t="n">
-        <v>77926</v>
+        <v>91370</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2689,21 +2689,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6437</v>
+        <v>2014</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>684631</v>
+        <v>684401</v>
       </c>
       <c r="R21" t="n">
-        <v>7393313</v>
+        <v>7393386</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2775,10 +2775,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120058977</v>
+        <v>120058975</v>
       </c>
       <c r="B22" t="n">
-        <v>91370</v>
+        <v>79527</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2787,25 +2787,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2014</v>
+        <v>6456</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2815,10 +2815,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>684401</v>
+        <v>684411</v>
       </c>
       <c r="R22" t="n">
-        <v>7393386</v>
+        <v>7393343</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2979,10 +2979,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120058978</v>
+        <v>120058981</v>
       </c>
       <c r="B24" t="n">
-        <v>91858</v>
+        <v>77474</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2991,25 +2991,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3019,10 +3019,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>684521</v>
+        <v>684561</v>
       </c>
       <c r="R24" t="n">
-        <v>7393403</v>
+        <v>7393342</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3081,10 +3081,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120058981</v>
+        <v>120058982</v>
       </c>
       <c r="B25" t="n">
-        <v>77474</v>
+        <v>77926</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3097,21 +3097,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6487</v>
+        <v>6437</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3121,10 +3121,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>684561</v>
+        <v>684559</v>
       </c>
       <c r="R25" t="n">
-        <v>7393342</v>
+        <v>7393341</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 36879-2023 artfynd.xlsx
+++ b/artfynd/A 36879-2023 artfynd.xlsx
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120058978</v>
+        <v>120058970</v>
       </c>
       <c r="B17" t="n">
-        <v>91858</v>
+        <v>79160</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2277,25 +2277,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>684521</v>
+        <v>684520</v>
       </c>
       <c r="R17" t="n">
-        <v>7393403</v>
+        <v>7393345</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2367,10 +2367,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120058970</v>
+        <v>120058977</v>
       </c>
       <c r="B18" t="n">
-        <v>79160</v>
+        <v>91370</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2383,21 +2383,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>2014</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2407,10 +2407,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>684520</v>
+        <v>684401</v>
       </c>
       <c r="R18" t="n">
-        <v>7393345</v>
+        <v>7393386</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2469,10 +2469,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120058983</v>
+        <v>120058978</v>
       </c>
       <c r="B19" t="n">
-        <v>77926</v>
+        <v>91858</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2481,25 +2481,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>684631</v>
+        <v>684521</v>
       </c>
       <c r="R19" t="n">
-        <v>7393313</v>
+        <v>7393403</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2571,7 +2571,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120058976</v>
+        <v>120058975</v>
       </c>
       <c r="B20" t="n">
         <v>79527</v>
@@ -2611,10 +2611,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>684521</v>
+        <v>684411</v>
       </c>
       <c r="R20" t="n">
-        <v>7393348</v>
+        <v>7393343</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2673,10 +2673,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120058977</v>
+        <v>120058976</v>
       </c>
       <c r="B21" t="n">
-        <v>91370</v>
+        <v>79527</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2685,25 +2685,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2014</v>
+        <v>6456</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>684401</v>
+        <v>684521</v>
       </c>
       <c r="R21" t="n">
-        <v>7393386</v>
+        <v>7393348</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2775,10 +2775,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120058975</v>
+        <v>120058983</v>
       </c>
       <c r="B22" t="n">
-        <v>79527</v>
+        <v>77926</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2787,25 +2787,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>6437</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2815,10 +2815,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>684411</v>
+        <v>684631</v>
       </c>
       <c r="R22" t="n">
-        <v>7393343</v>
+        <v>7393313</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 36879-2023 artfynd.xlsx
+++ b/artfynd/A 36879-2023 artfynd.xlsx
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120058970</v>
+        <v>120058978</v>
       </c>
       <c r="B17" t="n">
-        <v>79160</v>
+        <v>91858</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2277,25 +2277,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>684520</v>
+        <v>684521</v>
       </c>
       <c r="R17" t="n">
-        <v>7393345</v>
+        <v>7393403</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2367,10 +2367,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120058977</v>
+        <v>120058976</v>
       </c>
       <c r="B18" t="n">
-        <v>91370</v>
+        <v>79527</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2379,25 +2379,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2014</v>
+        <v>6456</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2407,10 +2407,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>684401</v>
+        <v>684521</v>
       </c>
       <c r="R18" t="n">
-        <v>7393386</v>
+        <v>7393348</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2469,10 +2469,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120058978</v>
+        <v>120058981</v>
       </c>
       <c r="B19" t="n">
-        <v>91858</v>
+        <v>77474</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2481,25 +2481,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>684521</v>
+        <v>684561</v>
       </c>
       <c r="R19" t="n">
-        <v>7393403</v>
+        <v>7393342</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2571,10 +2571,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120058975</v>
+        <v>120058982</v>
       </c>
       <c r="B20" t="n">
-        <v>79527</v>
+        <v>77926</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2583,25 +2583,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6456</v>
+        <v>6437</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2611,10 +2611,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>684411</v>
+        <v>684559</v>
       </c>
       <c r="R20" t="n">
-        <v>7393343</v>
+        <v>7393341</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2673,10 +2673,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120058976</v>
+        <v>120058983</v>
       </c>
       <c r="B21" t="n">
-        <v>79527</v>
+        <v>77926</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2685,25 +2685,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6456</v>
+        <v>6437</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>684521</v>
+        <v>684631</v>
       </c>
       <c r="R21" t="n">
-        <v>7393348</v>
+        <v>7393313</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2775,10 +2775,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120058983</v>
+        <v>120058977</v>
       </c>
       <c r="B22" t="n">
-        <v>77926</v>
+        <v>91370</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2791,21 +2791,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6437</v>
+        <v>2014</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2815,10 +2815,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>684631</v>
+        <v>684401</v>
       </c>
       <c r="R22" t="n">
-        <v>7393313</v>
+        <v>7393386</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2979,10 +2979,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120058981</v>
+        <v>120058975</v>
       </c>
       <c r="B24" t="n">
-        <v>77474</v>
+        <v>79527</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2991,25 +2991,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6487</v>
+        <v>6456</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3019,10 +3019,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>684561</v>
+        <v>684411</v>
       </c>
       <c r="R24" t="n">
-        <v>7393342</v>
+        <v>7393343</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3081,10 +3081,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120058982</v>
+        <v>120058970</v>
       </c>
       <c r="B25" t="n">
-        <v>77926</v>
+        <v>79160</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3097,21 +3097,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3121,10 +3121,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>684559</v>
+        <v>684520</v>
       </c>
       <c r="R25" t="n">
-        <v>7393341</v>
+        <v>7393345</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 36879-2023 artfynd.xlsx
+++ b/artfynd/A 36879-2023 artfynd.xlsx
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120058978</v>
+        <v>120058975</v>
       </c>
       <c r="B17" t="n">
-        <v>91858</v>
+        <v>79527</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2281,21 +2281,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6456</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>684521</v>
+        <v>684411</v>
       </c>
       <c r="R17" t="n">
-        <v>7393403</v>
+        <v>7393343</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2367,10 +2367,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120058976</v>
+        <v>120058970</v>
       </c>
       <c r="B18" t="n">
-        <v>79527</v>
+        <v>79160</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2379,25 +2379,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6456</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2407,10 +2407,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>684521</v>
+        <v>684520</v>
       </c>
       <c r="R18" t="n">
-        <v>7393348</v>
+        <v>7393345</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2469,10 +2469,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120058981</v>
+        <v>120058976</v>
       </c>
       <c r="B19" t="n">
-        <v>77474</v>
+        <v>79527</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2481,25 +2481,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6487</v>
+        <v>6456</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>684561</v>
+        <v>684521</v>
       </c>
       <c r="R19" t="n">
-        <v>7393342</v>
+        <v>7393348</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2571,7 +2571,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120058982</v>
+        <v>120058983</v>
       </c>
       <c r="B20" t="n">
         <v>77926</v>
@@ -2611,10 +2611,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>684559</v>
+        <v>684631</v>
       </c>
       <c r="R20" t="n">
-        <v>7393341</v>
+        <v>7393313</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2673,10 +2673,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120058983</v>
+        <v>120058978</v>
       </c>
       <c r="B21" t="n">
-        <v>77926</v>
+        <v>91858</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2685,25 +2685,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>684631</v>
+        <v>684521</v>
       </c>
       <c r="R21" t="n">
-        <v>7393313</v>
+        <v>7393403</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2775,10 +2775,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120058977</v>
+        <v>120058981</v>
       </c>
       <c r="B22" t="n">
-        <v>91370</v>
+        <v>77474</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2791,21 +2791,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2014</v>
+        <v>6487</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2815,10 +2815,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>684401</v>
+        <v>684561</v>
       </c>
       <c r="R22" t="n">
-        <v>7393386</v>
+        <v>7393342</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2877,10 +2877,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120058974</v>
+        <v>120058977</v>
       </c>
       <c r="B23" t="n">
-        <v>57473</v>
+        <v>91370</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2893,21 +2893,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>2014</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2917,10 +2917,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>684560</v>
+        <v>684401</v>
       </c>
       <c r="R23" t="n">
-        <v>7393340</v>
+        <v>7393386</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2979,10 +2979,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120058975</v>
+        <v>120058974</v>
       </c>
       <c r="B24" t="n">
-        <v>79527</v>
+        <v>57473</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2991,25 +2991,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6456</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3019,10 +3019,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>684411</v>
+        <v>684560</v>
       </c>
       <c r="R24" t="n">
-        <v>7393343</v>
+        <v>7393340</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3081,10 +3081,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120058970</v>
+        <v>120058982</v>
       </c>
       <c r="B25" t="n">
-        <v>79160</v>
+        <v>77926</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3097,21 +3097,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3121,10 +3121,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>684520</v>
+        <v>684559</v>
       </c>
       <c r="R25" t="n">
-        <v>7393345</v>
+        <v>7393341</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
